--- a/corr_matrix/residual_exam1B_1PL.xlsx
+++ b/corr_matrix/residual_exam1B_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>1B01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1111437814793846</v>
+        <v>-0.1111628879858404</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06701430404033766</v>
+        <v>-0.06702985476341049</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1016437629721749</v>
+        <v>-0.1016599894706993</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1726571826368182</v>
+        <v>-0.172653304947486</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.03311675174900856</v>
+        <v>-0.03312758882999379</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1092407839530017</v>
+        <v>-0.1092609968485064</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1591440098409504</v>
+        <v>0.159129046602773</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.05268756952342094</v>
+        <v>-0.05271037225176612</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.125935890297668</v>
+        <v>-0.1259616614611719</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005223265711515333</v>
+        <v>0.0005213224761397002</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02654319996018707</v>
+        <v>-0.02655886046758917</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4762919923392613</v>
+        <v>0.4762907941163679</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1051885245844405</v>
+        <v>-0.1052094674901334</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1519695849357435</v>
+        <v>-0.1519838601379588</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.09887625458926159</v>
+        <v>0.09888264390654235</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1111437814793846</v>
+        <v>-0.1111628879858404</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.08238863716941987</v>
+        <v>-0.08239101686745533</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.107697217428871</v>
+        <v>-0.107695868664535</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.02382572217405148</v>
+        <v>-0.02383908477450002</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01242334460722221</v>
+        <v>0.01243772646994551</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02987950801900317</v>
+        <v>-0.02988432144871863</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01178061604980335</v>
+        <v>-0.01181324687285918</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1194654852514066</v>
+        <v>-0.1194858786845756</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1616836275687282</v>
+        <v>-0.1616641398747599</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1547882759424923</v>
+        <v>-0.1547827024421936</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01069724680835356</v>
+        <v>-0.01072026919724593</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1086248128395817</v>
+        <v>-0.1086453391976537</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04283402668095449</v>
+        <v>0.04282561849977214</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03110645580326281</v>
+        <v>0.03108752279019163</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1794819162176263</v>
+        <v>-0.1794813181393384</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.06701430404033766</v>
+        <v>-0.06702985476341049</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.08238863716941987</v>
+        <v>-0.08239101686745533</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06939439990708375</v>
+        <v>-0.06937902265439892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03491858880997589</v>
+        <v>0.03491156720692443</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1330940089930179</v>
+        <v>-0.1330759680175339</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.002974607920159734</v>
+        <v>-0.002967403675387339</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2670897561144625</v>
+        <v>-0.2671056308412899</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02973683339784821</v>
+        <v>0.02973443725775925</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002844432174150559</v>
+        <v>0.002865217484328072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00414848510550838</v>
+        <v>0.004145512858957898</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3558801624062151</v>
+        <v>-0.3558851276913642</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04096340777870688</v>
+        <v>0.0409495419757297</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01715579165034402</v>
+        <v>-0.01715196612549821</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2291874409924969</v>
+        <v>-0.2291890933123566</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08886871893316993</v>
+        <v>0.088870927161223</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1016437629721749</v>
+        <v>-0.1016599894706993</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.107697217428871</v>
+        <v>-0.107695868664535</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06939439990708375</v>
+        <v>-0.06937902265439892</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1075962889672896</v>
+        <v>0.1075865072397353</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.09231674333197337</v>
+        <v>-0.0922902107179213</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01562667382368436</v>
+        <v>-0.01561414377734407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05988679956195012</v>
+        <v>0.05987606377884597</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1014082175000548</v>
+        <v>-0.1014074153226698</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005303001321165588</v>
+        <v>0.005332676895320553</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2611634864310021</v>
+        <v>-0.2611579022265949</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1491316466152947</v>
+        <v>-0.1491319076313571</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0978334732424268</v>
+        <v>-0.09784990356389181</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1381524642850648</v>
+        <v>-0.1381449520644133</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1007999743362276</v>
+        <v>-0.1007972509644908</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.03765933899926797</v>
+        <v>-0.03765630646284159</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1726571826368182</v>
+        <v>-0.172653304947486</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.02382572217405148</v>
+        <v>-0.02383908477450002</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03491858880997589</v>
+        <v>0.03491156720692443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1075962889672896</v>
+        <v>0.1075865072397353</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2819942354732897</v>
+        <v>-0.2819998762747512</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1580593462283052</v>
+        <v>-0.1580565742459639</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1235569911987022</v>
+        <v>-0.1235664563609212</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.08347242584571517</v>
+        <v>-0.08347250581912756</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.09161489137837173</v>
+        <v>-0.09159625586714439</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.153051062658213</v>
+        <v>-0.1530278608294156</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05917337944900557</v>
+        <v>-0.05919472149515344</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08288870984467597</v>
+        <v>0.08288827741482736</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06319017510377863</v>
+        <v>-0.06318902088405959</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.007775440107733656</v>
+        <v>-0.007804285171296564</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0968529023278261</v>
+        <v>-0.09686673418112472</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.03311675174900856</v>
+        <v>-0.03312758882999379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01242334460722221</v>
+        <v>0.01243772646994551</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1330940089930179</v>
+        <v>-0.1330759680175339</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09231674333197337</v>
+        <v>-0.0922902107179213</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2819942354732897</v>
+        <v>-0.2819998762747512</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.004249969917022583</v>
+        <v>-0.004222328126339506</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1252769937287235</v>
+        <v>-0.1252762271565957</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1588287218942641</v>
+        <v>-0.1588115349410054</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0002858016527490185</v>
+        <v>-0.0002389510157841454</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.07705604777925663</v>
+        <v>-0.07704063622785524</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0006554589968974445</v>
+        <v>-0.0006453874877949249</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1229313705780853</v>
+        <v>-0.1229486455111208</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01294065914271035</v>
+        <v>-0.01292384936580522</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.09714244930564615</v>
+        <v>-0.0971306261579036</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1332206505400449</v>
+        <v>-0.1332126138290922</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1092407839530017</v>
+        <v>-0.1092609968485064</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.02987950801900317</v>
+        <v>-0.02988432144871863</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002974607920159734</v>
+        <v>-0.002967403675387339</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01562667382368436</v>
+        <v>-0.01561414377734407</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1580593462283052</v>
+        <v>-0.1580565742459639</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.004249969917022583</v>
+        <v>-0.004222328126339506</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05784045791973867</v>
+        <v>-0.05786133882503629</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1517295949471881</v>
+        <v>0.151723281300634</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1447589495606224</v>
+        <v>-0.1447355731503842</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007868818312761445</v>
+        <v>0.007876083497688971</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.069204998546212</v>
+        <v>-0.0692101209326425</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2991232852919218</v>
+        <v>-0.299141822134492</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.07250115830719819</v>
+        <v>-0.07250293418464433</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1253117130090753</v>
+        <v>-0.125312220488025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2086854230712413</v>
+        <v>-0.2086714468488429</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1591440098409504</v>
+        <v>0.159129046602773</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01178061604980335</v>
+        <v>-0.01181324687285918</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2670897561144625</v>
+        <v>-0.2671056308412899</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05988679956195012</v>
+        <v>0.05987606377884597</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1235569911987022</v>
+        <v>-0.1235664563609212</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1252769937287235</v>
+        <v>-0.1252762271565957</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.05784045791973867</v>
+        <v>-0.05786133882503629</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.02237782270304743</v>
+        <v>-0.02241004873206406</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1756992659602718</v>
+        <v>-0.17570266901517</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.01766891663801169</v>
+        <v>-0.01766556291151097</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01477485961428691</v>
+        <v>0.01474291568631675</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0466675741061628</v>
+        <v>0.04665275093901559</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0004114091944419991</v>
+        <v>-0.0004331324077327335</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1816691703373281</v>
+        <v>-0.1817034425899755</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00278827587458455</v>
+        <v>0.002793645632956104</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.05268756952342094</v>
+        <v>-0.05271037225176612</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1194654852514066</v>
+        <v>-0.1194858786845756</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02973683339784821</v>
+        <v>0.02973443725775925</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1014082175000548</v>
+        <v>-0.1014074153226698</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.08347242584571517</v>
+        <v>-0.08347250581912756</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1588287218942641</v>
+        <v>-0.1588115349410054</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1517295949471881</v>
+        <v>0.151723281300634</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.02237782270304743</v>
+        <v>-0.02241004873206406</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1337619779377607</v>
+        <v>-0.1337518403733821</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1051712314998253</v>
+        <v>-0.1051623844994176</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09639605107675044</v>
+        <v>-0.09641614089075655</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1529791500164981</v>
+        <v>-0.1530007696313453</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04493125502640629</v>
+        <v>-0.04494401477127409</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1527321704106118</v>
+        <v>-0.1527485681564348</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.08563577915438207</v>
+        <v>0.08565000162536614</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.125935890297668</v>
+        <v>-0.1259616614611719</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1616836275687282</v>
+        <v>-0.1616641398747599</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002844432174150559</v>
+        <v>0.002865217484328072</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005303001321165588</v>
+        <v>0.005332676895320553</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09161489137837173</v>
+        <v>-0.09159625586714439</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0002858016527490185</v>
+        <v>-0.0002389510157841454</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1447589495606224</v>
+        <v>-0.1447355731503842</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1756992659602718</v>
+        <v>-0.17570266901517</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1337619779377607</v>
+        <v>-0.1337518403733821</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1426675938175593</v>
+        <v>0.1426725264848649</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2455708868541774</v>
+        <v>-0.245549401455477</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02695089641389275</v>
+        <v>-0.02697600455809059</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04597073898196206</v>
+        <v>0.04598057374554308</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1790305326222851</v>
+        <v>-0.1790021731705926</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.09364186757211337</v>
+        <v>-0.09361601543486155</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0005223265711515333</v>
+        <v>0.0005213224761397002</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1547882759424923</v>
+        <v>-0.1547827024421936</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00414848510550838</v>
+        <v>0.004145512858957898</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2611634864310021</v>
+        <v>-0.2611579022265949</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.153051062658213</v>
+        <v>-0.1530278608294156</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.07705604777925663</v>
+        <v>-0.07704063622785524</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007868818312761445</v>
+        <v>0.007876083497688971</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01766891663801169</v>
+        <v>-0.01766556291151097</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1051712314998253</v>
+        <v>-0.1051623844994176</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1426675938175593</v>
+        <v>0.1426725264848649</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1892177294698135</v>
+        <v>-0.1892136572933769</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.009884435474766785</v>
+        <v>-0.00988852733095379</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1413530330550332</v>
+        <v>-0.1413498481472804</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.04704728600169104</v>
+        <v>-0.04704634624840399</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1367969939686068</v>
+        <v>-0.1367824571474924</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.02654319996018707</v>
+        <v>-0.02655886046758917</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.01069724680835356</v>
+        <v>-0.01072026919724593</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3558801624062151</v>
+        <v>-0.3558851276913642</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1491316466152947</v>
+        <v>-0.1491319076313571</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05917337944900557</v>
+        <v>-0.05919472149515344</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0006554589968974445</v>
+        <v>-0.0006453874877949249</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.069204998546212</v>
+        <v>-0.0692101209326425</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01477485961428691</v>
+        <v>0.01474291568631675</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.09639605107675044</v>
+        <v>-0.09641614089075655</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2455708868541774</v>
+        <v>-0.245549401455477</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1892177294698135</v>
+        <v>-0.1892136572933769</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1278126608517392</v>
+        <v>-0.1278326467628035</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.184856805291161</v>
+        <v>-0.1848678495412034</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6041105678113661</v>
+        <v>0.6041012928033229</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1097228034767514</v>
+        <v>-0.1097264907366076</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4762919923392613</v>
+        <v>0.4762907941163679</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1086248128395817</v>
+        <v>-0.1086453391976537</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04096340777870688</v>
+        <v>0.0409495419757297</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0978334732424268</v>
+        <v>-0.09784990356389181</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08288870984467597</v>
+        <v>0.08288827741482736</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1229313705780853</v>
+        <v>-0.1229486455111208</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2991232852919218</v>
+        <v>-0.299141822134492</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0466675741061628</v>
+        <v>0.04665275093901559</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1529791500164981</v>
+        <v>-0.1530007696313453</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02695089641389275</v>
+        <v>-0.02697600455809059</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009884435474766785</v>
+        <v>-0.00988852733095379</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1278126608517392</v>
+        <v>-0.1278326467628035</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1221478505143823</v>
+        <v>0.1221312378294548</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1532750755964814</v>
+        <v>-0.1532942169544988</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.004276986130433195</v>
+        <v>-0.004277874987878796</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1051885245844405</v>
+        <v>-0.1052094674901334</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04283402668095449</v>
+        <v>0.04282561849977214</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01715579165034402</v>
+        <v>-0.01715196612549821</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1381524642850648</v>
+        <v>-0.1381449520644133</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06319017510377863</v>
+        <v>-0.06318902088405959</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.01294065914271035</v>
+        <v>-0.01292384936580522</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07250115830719819</v>
+        <v>-0.07250293418464433</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0004114091944419991</v>
+        <v>-0.0004331324077327335</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.04493125502640629</v>
+        <v>-0.04494401477127409</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04597073898196206</v>
+        <v>0.04598057374554308</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1413530330550332</v>
+        <v>-0.1413498481472804</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.184856805291161</v>
+        <v>-0.1848678495412034</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1221478505143823</v>
+        <v>0.1221312378294548</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1699150379258641</v>
+        <v>-0.1699210356318208</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1178992200997534</v>
+        <v>-0.1178907389171648</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1519695849357435</v>
+        <v>-0.1519838601379588</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03110645580326281</v>
+        <v>0.03108752279019163</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2291874409924969</v>
+        <v>-0.2291890933123566</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1007999743362276</v>
+        <v>-0.1007972509644908</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.007775440107733656</v>
+        <v>-0.007804285171296564</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.09714244930564615</v>
+        <v>-0.0971306261579036</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1253117130090753</v>
+        <v>-0.125312220488025</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1816691703373281</v>
+        <v>-0.1817034425899755</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1527321704106118</v>
+        <v>-0.1527485681564348</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1790305326222851</v>
+        <v>-0.1790021731705926</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.04704728600169104</v>
+        <v>-0.04704634624840399</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6041105678113661</v>
+        <v>0.6041012928033229</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1532750755964814</v>
+        <v>-0.1532942169544988</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1699150379258641</v>
+        <v>-0.1699210356318208</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1604773383033816</v>
+        <v>-0.1604884152138747</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09887625458926159</v>
+        <v>0.09888264390654235</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1794819162176263</v>
+        <v>-0.1794813181393384</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08886871893316993</v>
+        <v>0.088870927161223</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03765933899926797</v>
+        <v>-0.03765630646284159</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0968529023278261</v>
+        <v>-0.09686673418112472</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1332206505400449</v>
+        <v>-0.1332126138290922</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2086854230712413</v>
+        <v>-0.2086714468488429</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00278827587458455</v>
+        <v>0.002793645632956104</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08563577915438207</v>
+        <v>0.08565000162536614</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09364186757211337</v>
+        <v>-0.09361601543486155</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1367969939686068</v>
+        <v>-0.1367824571474924</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1097228034767514</v>
+        <v>-0.1097264907366076</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.004276986130433195</v>
+        <v>-0.004277874987878796</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1178992200997534</v>
+        <v>-0.1178907389171648</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1604773383033816</v>
+        <v>-0.1604884152138747</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>

--- a/corr_matrix/residual_exam1B_1PL.xlsx
+++ b/corr_matrix/residual_exam1B_1PL.xlsx
@@ -1,37 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+  <si>
+    <t>1B01</t>
+  </si>
+  <si>
+    <t>1B02</t>
+  </si>
+  <si>
+    <t>1B03</t>
+  </si>
+  <si>
+    <t>1B04</t>
+  </si>
+  <si>
+    <t>1B05</t>
+  </si>
+  <si>
+    <t>1B06</t>
+  </si>
+  <si>
+    <t>1B07</t>
+  </si>
+  <si>
+    <t>1B08</t>
+  </si>
+  <si>
+    <t>1B09</t>
+  </si>
+  <si>
+    <t>1B10</t>
+  </si>
+  <si>
+    <t>1B11</t>
+  </si>
+  <si>
+    <t>1B12</t>
+  </si>
+  <si>
+    <t>1B13</t>
+  </si>
+  <si>
+    <t>1B14</t>
+  </si>
+  <si>
+    <t>1B15</t>
+  </si>
+  <si>
+    <t>1B16</t>
+  </si>
+  <si>
+    <t>question_id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +105,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,982 +421,912 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>question_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>1B01</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>1B02</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>1B03</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>1B04</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>1B05</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>1B06</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>1B07</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>1B08</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>1B09</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>1B10</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>1B11</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>1B12</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>1B13</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>1B14</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>1B15</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>1B16</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>1B01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>-0.1111628879858404</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.06702985476341049</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>-0.06702985476341046</v>
+      </c>
+      <c r="E2">
         <v>-0.1016599894706993</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-0.172653304947486</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>-0.03312758882999379</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>-0.1092609968485064</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>0.159129046602773</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>-0.05271037225176612</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>-0.1259616614611719</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.0005213224761397002</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>-0.02655886046758917</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.4762907941163679</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>-0.1052094674901334</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>-0.1519838601379588</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>0.09888264390654235</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>1B02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
         <v>-0.1111628879858404</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>-0.08239101686745533</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>-0.107695868664535</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>-0.02383908477450002</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.01243772646994551</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>-0.02988432144871863</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>-0.01181324687285918</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>-0.1194858786845756</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>-0.1616641398747599</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>-0.1547827024421936</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>-0.01072026919724593</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>-0.1086453391976537</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.04282561849977214</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>0.03108752279019163</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>-0.1794813181393384</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>1B03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-0.06702985476341049</v>
-      </c>
-      <c r="C4" t="n">
+    <row r="4" spans="1:17">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-0.06702985476341046</v>
+      </c>
+      <c r="C4">
         <v>-0.08239101686745533</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>-0.06937902265439892</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.03491156720692443</v>
       </c>
-      <c r="G4" t="n">
-        <v>-0.1330759680175339</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="G4">
+        <v>-0.133075968017534</v>
+      </c>
+      <c r="H4">
         <v>-0.002967403675387339</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>-0.2671056308412899</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.02973443725775925</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.002865217484328072</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="J4">
+        <v>0.02973443725775926</v>
+      </c>
+      <c r="K4">
+        <v>0.002865217484328064</v>
+      </c>
+      <c r="L4">
         <v>0.004145512858957898</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>-0.3558851276913642</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.0409495419757297</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>-0.01715196612549821</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>-0.2291890933123566</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0.088870927161223</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>1B04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="Q4">
+        <v>0.08887092716122301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>-0.1016599894706993</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>-0.107695868664535</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>-0.06937902265439892</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0.1075865072397353</v>
       </c>
-      <c r="G5" t="n">
-        <v>-0.0922902107179213</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G5">
+        <v>-0.09229021071792133</v>
+      </c>
+      <c r="H5">
         <v>-0.01561414377734407</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>0.05987606377884597</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>-0.1014074153226698</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.005332676895320553</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K5">
+        <v>0.005332676895320521</v>
+      </c>
+      <c r="L5">
         <v>-0.2611579022265949</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>-0.1491319076313571</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>-0.09784990356389181</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>-0.1381449520644133</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>-0.1007972509644908</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.03765630646284159</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>1B05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="Q5">
+        <v>-0.03765630646284161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>-0.172653304947486</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>-0.02383908477450002</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.03491156720692443</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.1075865072397353</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>-0.2819998762747512</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>-0.1580565742459639</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>-0.1235664563609212</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>-0.08347250581912756</v>
       </c>
-      <c r="K6" t="n">
-        <v>-0.09159625586714439</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K6">
+        <v>-0.09159625586714429</v>
+      </c>
+      <c r="L6">
         <v>-0.1530278608294156</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>-0.05919472149515344</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.08288827741482736</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>-0.06318902088405959</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>-0.007804285171296564</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>-0.09686673418112472</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>1B06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:17">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>-0.03312758882999379</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.01243772646994551</v>
       </c>
-      <c r="D7" t="n">
-        <v>-0.1330759680175339</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.0922902107179213</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="D7">
+        <v>-0.133075968017534</v>
+      </c>
+      <c r="E7">
+        <v>-0.09229021071792133</v>
+      </c>
+      <c r="F7">
         <v>-0.2819998762747512</v>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.004222328126339506</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>-0.004222328126339525</v>
+      </c>
+      <c r="I7">
         <v>-0.1252762271565957</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>-0.1588115349410054</v>
       </c>
-      <c r="K7" t="n">
-        <v>-0.0002389510157841454</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K7">
+        <v>-0.0002389510157841526</v>
+      </c>
+      <c r="L7">
         <v>-0.07704063622785524</v>
       </c>
-      <c r="M7" t="n">
-        <v>-0.0006453874877949249</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="M7">
+        <v>-0.0006453874877949406</v>
+      </c>
+      <c r="N7">
         <v>-0.1229486455111208</v>
       </c>
-      <c r="O7" t="n">
-        <v>-0.01292384936580522</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="O7">
+        <v>-0.01292384936580523</v>
+      </c>
+      <c r="P7">
         <v>-0.0971306261579036</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>-0.1332126138290922</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>1B07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:17">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>-0.1092609968485064</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>-0.02988432144871863</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>-0.002967403675387339</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>-0.01561414377734407</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>-0.1580565742459639</v>
       </c>
-      <c r="G8" t="n">
-        <v>-0.004222328126339506</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="G8">
+        <v>-0.004222328126339525</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>-0.05786133882503629</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>0.151723281300634</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>-0.1447355731503842</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.007876083497688971</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="L8">
+        <v>0.007876083497688976</v>
+      </c>
+      <c r="M8">
         <v>-0.0692101209326425</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>-0.299141822134492</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>-0.07250293418464433</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>-0.125312220488025</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>-0.2086714468488429</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>1B08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:17">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>0.159129046602773</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>-0.01181324687285918</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>-0.2671056308412899</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.05987606377884597</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>-0.1235664563609212</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>-0.1252762271565957</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>-0.05786133882503629</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.02241004873206406</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>-0.02241004873206405</v>
+      </c>
+      <c r="K9">
         <v>-0.17570266901517</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>-0.01766556291151097</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.01474291568631675</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.04665275093901559</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="N9">
+        <v>0.04665275093901561</v>
+      </c>
+      <c r="O9">
         <v>-0.0004331324077327335</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>-0.1817034425899755</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>0.002793645632956104</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>1B09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:17">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
         <v>-0.05271037225176612</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>-0.1194858786845756</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.02973443725775925</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10">
+        <v>0.02973443725775926</v>
+      </c>
+      <c r="E10">
         <v>-0.1014074153226698</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>-0.08347250581912756</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>-0.1588115349410054</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.151723281300634</v>
       </c>
-      <c r="I10" t="n">
-        <v>-0.02241004873206406</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.1337518403733821</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I10">
+        <v>-0.02241004873206405</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>-0.133751840373382</v>
+      </c>
+      <c r="L10">
         <v>-0.1051623844994176</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>-0.09641614089075655</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>-0.1530007696313453</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>-0.04494401477127409</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>-0.1527485681564348</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>0.08565000162536614</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>1B10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:17">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
         <v>-0.1259616614611719</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>-0.1616641398747599</v>
       </c>
-      <c r="D11" t="n">
-        <v>0.002865217484328072</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.005332676895320553</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.09159625586714439</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.0002389510157841454</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="D11">
+        <v>0.002865217484328064</v>
+      </c>
+      <c r="E11">
+        <v>0.005332676895320521</v>
+      </c>
+      <c r="F11">
+        <v>-0.09159625586714429</v>
+      </c>
+      <c r="G11">
+        <v>-0.0002389510157841526</v>
+      </c>
+      <c r="H11">
         <v>-0.1447355731503842</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>-0.17570266901517</v>
       </c>
-      <c r="J11" t="n">
-        <v>-0.1337518403733821</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J11">
+        <v>-0.133751840373382</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>0.1426725264848649</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>-0.245549401455477</v>
       </c>
-      <c r="N11" t="n">
-        <v>-0.02697600455809059</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.04598057374554308</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11">
+        <v>-0.02697600455809061</v>
+      </c>
+      <c r="O11">
+        <v>0.04598057374554306</v>
+      </c>
+      <c r="P11">
         <v>-0.1790021731705926</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>-0.09361601543486155</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>1B11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:17">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
         <v>0.0005213224761397002</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>-0.1547827024421936</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.004145512858957898</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>-0.2611579022265949</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>-0.1530278608294156</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>-0.07704063622785524</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.007876083497688971</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="H12">
+        <v>0.007876083497688976</v>
+      </c>
+      <c r="I12">
         <v>-0.01766556291151097</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>-0.1051623844994176</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.1426725264848649</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
         <v>-0.1892136572933769</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>-0.00988852733095379</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>-0.1413498481472804</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>-0.04704634624840399</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>-0.1367824571474924</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>1B12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:17">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>-0.02655886046758917</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>-0.01072026919724593</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>-0.3558851276913642</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>-0.1491319076313571</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>-0.05919472149515344</v>
       </c>
-      <c r="G13" t="n">
-        <v>-0.0006453874877949249</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="G13">
+        <v>-0.0006453874877949406</v>
+      </c>
+      <c r="H13">
         <v>-0.0692101209326425</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>0.01474291568631675</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>-0.09641614089075655</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>-0.245549401455477</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>-0.1892136572933769</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>-0.1278326467628035</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>-0.1848678495412034</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>0.6041012928033229</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>-0.1097264907366076</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>1B13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:17">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
         <v>0.4762907941163679</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>-0.1086453391976537</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.0409495419757297</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>-0.09784990356389181</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.08288827741482736</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>-0.1229486455111208</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>-0.299141822134492</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.04665275093901559</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I14">
+        <v>0.04665275093901561</v>
+      </c>
+      <c r="J14">
         <v>-0.1530007696313453</v>
       </c>
-      <c r="K14" t="n">
-        <v>-0.02697600455809059</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K14">
+        <v>-0.02697600455809061</v>
+      </c>
+      <c r="L14">
         <v>-0.00988852733095379</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>-0.1278326467628035</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
         <v>0.1221312378294548</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>-0.1532942169544988</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>-0.004277874987878796</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>1B14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:17">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <v>-0.1052094674901334</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>0.04282561849977214</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>-0.01715196612549821</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>-0.1381449520644133</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>-0.06318902088405959</v>
       </c>
-      <c r="G15" t="n">
-        <v>-0.01292384936580522</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="G15">
+        <v>-0.01292384936580523</v>
+      </c>
+      <c r="H15">
         <v>-0.07250293418464433</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>-0.0004331324077327335</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>-0.04494401477127409</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.04598057374554308</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K15">
+        <v>0.04598057374554306</v>
+      </c>
+      <c r="L15">
         <v>-0.1413498481472804</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>-0.1848678495412034</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.1221312378294548</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
         <v>-0.1699210356318208</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>-0.1178907389171648</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>1B15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
         <v>-0.1519838601379588</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.03108752279019163</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-0.2291890933123566</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>-0.1007972509644908</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>-0.007804285171296564</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>-0.0971306261579036</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>-0.125312220488025</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>-0.1817034425899755</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>-0.1527485681564348</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>-0.1790021731705926</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>-0.04704634624840399</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>0.6041012928033229</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>-0.1532942169544988</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>-0.1699210356318208</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
         <v>-0.1604884152138747</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>1B16</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:17">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>0.09888264390654235</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>-0.1794813181393384</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.088870927161223</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.03765630646284159</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="D17">
+        <v>0.08887092716122301</v>
+      </c>
+      <c r="E17">
+        <v>-0.03765630646284161</v>
+      </c>
+      <c r="F17">
         <v>-0.09686673418112472</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>-0.1332126138290922</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>-0.2086714468488429</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>0.002793645632956104</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>0.08565000162536614</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>-0.09361601543486155</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>-0.1367824571474924</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>-0.1097264907366076</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>-0.004277874987878796</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>-0.1178907389171648</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>-0.1604884152138747</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>